--- a/data/excel/२०२६/०४/०३.xlsx
+++ b/data/excel/२०२६/०४/०३.xlsx
@@ -16,22 +16,34 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
   <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Max Price</t>
+  </si>
+  <si>
     <t>Min Price</t>
   </si>
   <si>
     <t>Avg Price</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Max Price</t>
+    <t>केजी</t>
+  </si>
+  <si>
+    <t>७०.००</t>
+  </si>
+  <si>
+    <t>६०.००</t>
+  </si>
+  <si>
+    <t>६५.००</t>
   </si>
   <si>
     <t>२०२६-०४-०३</t>
@@ -40,18 +52,6 @@
     <t>गोलभेडा ठूलो(भारतीय)</t>
   </si>
   <si>
-    <t>केजी</t>
-  </si>
-  <si>
-    <t>७०.००</t>
-  </si>
-  <si>
-    <t>६०.००</t>
-  </si>
-  <si>
-    <t>६५.००</t>
-  </si>
-  <si>
     <t>गोलभेडा सानो(लोकल)</t>
   </si>
   <si>
@@ -67,6 +67,12 @@
     <t>२७.००</t>
   </si>
   <si>
+    <t>३०.००</t>
+  </si>
+  <si>
+    <t>गोलभेडा सानो(भारतीय)</t>
+  </si>
+  <si>
     <t>के जी</t>
   </si>
   <si>
@@ -76,12 +82,6 @@
     <t>२५.००</t>
   </si>
   <si>
-    <t>३०.००</t>
-  </si>
-  <si>
-    <t>गोलभेडा सानो(भारतीय)</t>
-  </si>
-  <si>
     <t>गोलभेडा सानो(तराई)</t>
   </si>
   <si>
@@ -100,13 +100,16 @@
     <t>१७.५०</t>
   </si>
   <si>
+    <t>२३.००</t>
+  </si>
+  <si>
+    <t>२१.५०</t>
+  </si>
+  <si>
     <t>आलु रातो(भारतीय)</t>
   </si>
   <si>
-    <t>२३.००</t>
-  </si>
-  <si>
-    <t>२१.५०</t>
+    <t>३६.००</t>
   </si>
   <si>
     <t>प्याज सुकेको (भारतीय)</t>
@@ -118,39 +121,36 @@
     <t>३५.००</t>
   </si>
   <si>
-    <t>३६.००</t>
-  </si>
-  <si>
     <t>गाजर(लोकल)</t>
   </si>
   <si>
+    <t>गाजर(तराई)</t>
+  </si>
+  <si>
     <t>१६.००</t>
   </si>
   <si>
     <t>२०.५०</t>
   </si>
   <si>
-    <t>गाजर(तराई)</t>
+    <t>बन्दा(लोकल)</t>
   </si>
   <si>
     <t>२७.१४</t>
   </si>
   <si>
-    <t>बन्दा(लोकल)</t>
-  </si>
-  <si>
     <t>बन्दा(नरिवल)</t>
   </si>
   <si>
+    <t>काउली स्थानिय</t>
+  </si>
+  <si>
     <t>५०.००</t>
   </si>
   <si>
     <t>५५.००</t>
   </si>
   <si>
-    <t>काउली स्थानिय</t>
-  </si>
-  <si>
     <t>स्थानीय काउली(ज्यापु)</t>
   </si>
   <si>
@@ -211,18 +211,18 @@
     <t>टाटे सिमी</t>
   </si>
   <si>
+    <t>तितो करेला</t>
+  </si>
+  <si>
+    <t>१६०.००</t>
+  </si>
+  <si>
+    <t>१५०.००</t>
+  </si>
+  <si>
     <t>१५५.००</t>
   </si>
   <si>
-    <t>तितो करेला</t>
-  </si>
-  <si>
-    <t>१६०.००</t>
-  </si>
-  <si>
-    <t>१५०.००</t>
-  </si>
-  <si>
     <t>लौका</t>
   </si>
   <si>
@@ -247,15 +247,15 @@
     <t>हरियो फर्सी(डल्लो)</t>
   </si>
   <si>
+    <t>१३०.००</t>
+  </si>
+  <si>
+    <t>१२५.००</t>
+  </si>
+  <si>
     <t>भिण्डी</t>
   </si>
   <si>
-    <t>१३०.००</t>
-  </si>
-  <si>
-    <t>१२५.००</t>
-  </si>
-  <si>
     <t>सखरखण्ड</t>
   </si>
   <si>
@@ -283,21 +283,21 @@
     <t>चमसूरको साग</t>
   </si>
   <si>
+    <t>४५.००</t>
+  </si>
+  <si>
     <t>तोरीको साग</t>
   </si>
   <si>
-    <t>४५.००</t>
-  </si>
-  <si>
     <t>मेथीको साग</t>
   </si>
   <si>
+    <t>प्याज हरियो</t>
+  </si>
+  <si>
     <t>७६.००</t>
   </si>
   <si>
-    <t>प्याज हरियो</t>
-  </si>
-  <si>
     <t>बकूला</t>
   </si>
   <si>
@@ -310,6 +310,9 @@
     <t>१४०.००</t>
   </si>
   <si>
+    <t>३७६.००</t>
+  </si>
+  <si>
     <t>च्याउ(डल्ले)</t>
   </si>
   <si>
@@ -319,9 +322,6 @@
     <t>३५०.००</t>
   </si>
   <si>
-    <t>३७६.००</t>
-  </si>
-  <si>
     <t>३००.००</t>
   </si>
   <si>
@@ -334,6 +334,9 @@
     <t>राजा च्याउ</t>
   </si>
   <si>
+    <t>सिताके च्याउ</t>
+  </si>
+  <si>
     <t>१०००.००</t>
   </si>
   <si>
@@ -343,27 +346,24 @@
     <t>९००.००</t>
   </si>
   <si>
-    <t>सिताके च्याउ</t>
+    <t>४२५.००</t>
+  </si>
+  <si>
+    <t>३७५.००</t>
   </si>
   <si>
     <t>कुरीलो</t>
   </si>
   <si>
-    <t>४२५.००</t>
-  </si>
-  <si>
-    <t>३७५.००</t>
-  </si>
-  <si>
     <t>न्यूरो</t>
   </si>
   <si>
+    <t>ब्रोकाउली</t>
+  </si>
+  <si>
     <t>७७.५०</t>
   </si>
   <si>
-    <t>ब्रोकाउली</t>
-  </si>
-  <si>
     <t>चुकुन्दर</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>सेलरी</t>
   </si>
   <si>
+    <t>पार्सले</t>
+  </si>
+  <si>
+    <t>२००.००</t>
+  </si>
+  <si>
     <t>१७५.००</t>
   </si>
   <si>
-    <t>पार्सले</t>
-  </si>
-  <si>
-    <t>२००.००</t>
-  </si>
-  <si>
     <t>सौफको साग</t>
   </si>
   <si>
@@ -430,33 +430,33 @@
     <t>गुन्दुक</t>
   </si>
   <si>
+    <t>२२५.००</t>
+  </si>
+  <si>
+    <t>स्याउ(झोले)</t>
+  </si>
+  <si>
     <t>२५०.००</t>
   </si>
   <si>
-    <t>२२५.००</t>
-  </si>
-  <si>
-    <t>स्याउ(झोले)</t>
+    <t>२७५.००</t>
   </si>
   <si>
     <t>स्याउ(फूजी)</t>
   </si>
   <si>
-    <t>२७५.००</t>
+    <t>२१०.००</t>
+  </si>
+  <si>
+    <t>केरा</t>
+  </si>
+  <si>
+    <t>दर्जन</t>
   </si>
   <si>
     <t>२२०.००</t>
   </si>
   <si>
-    <t>२१०.००</t>
-  </si>
-  <si>
-    <t>केरा</t>
-  </si>
-  <si>
-    <t>दर्जन</t>
-  </si>
-  <si>
     <t>कागती</t>
   </si>
   <si>
@@ -472,15 +472,15 @@
     <t>अंगुर(हरियो)</t>
   </si>
   <si>
+    <t>अंगुर(कालो)</t>
+  </si>
+  <si>
     <t>३३०.००</t>
   </si>
   <si>
     <t>३४०.००</t>
   </si>
   <si>
-    <t>अंगुर(कालो)</t>
-  </si>
-  <si>
     <t>सुन्तला(भारतीय)</t>
   </si>
   <si>
@@ -493,12 +493,12 @@
     <t>प्रति गोटा</t>
   </si>
   <si>
+    <t>काक्रो(लोकल)</t>
+  </si>
+  <si>
     <t>४२.००</t>
   </si>
   <si>
-    <t>काक्रो(लोकल)</t>
-  </si>
-  <si>
     <t>काक्रो(हाइब्रीड)</t>
   </si>
   <si>
@@ -550,12 +550,12 @@
     <t>अदुवा</t>
   </si>
   <si>
+    <t>खु्र्सानी सुकेको</t>
+  </si>
+  <si>
     <t>४५०.००</t>
   </si>
   <si>
-    <t>खु्र्सानी सुकेको</t>
-  </si>
-  <si>
     <t>खु्र्सानी हरियो</t>
   </si>
   <si>
@@ -571,12 +571,12 @@
     <t>भेडे खु्र्सानी</t>
   </si>
   <si>
+    <t>लसुन हरियो</t>
+  </si>
+  <si>
     <t>७६.६७</t>
   </si>
   <si>
-    <t>लसुन हरियो</t>
-  </si>
-  <si>
     <t>हरियो धनिया</t>
   </si>
   <si>
@@ -604,10 +604,10 @@
     <t>३२०.००</t>
   </si>
   <si>
+    <t>२९५.००</t>
+  </si>
+  <si>
     <t>ताजा माछा(बचुवा)</t>
-  </si>
-  <si>
-    <t>२९५.००</t>
   </si>
   <si>
     <t>३१०.००</t>
@@ -922,47 +922,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -982,39 +982,39 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
         <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
       </c>
       <c r="F5" t="s">
         <v>23</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1042,47 +1042,47 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
         <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>29</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
         <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>35</v>
@@ -1091,67 +1091,67 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
         <v>6</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" t="s">
         <v>38</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
         <v>40</v>
-      </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
         <v>26</v>
@@ -1162,39 +1162,39 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" t="s">
         <v>44</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
         <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D14" t="s">
         <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
         <v>47</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
         <v>48</v>
@@ -1222,27 +1222,27 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
         <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E16" t="s">
         <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
         <v>50</v>
@@ -1251,18 +1251,18 @@
         <v>13</v>
       </c>
       <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
         <v>9</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
         <v>51</v>
@@ -1274,7 +1274,7 @@
         <v>46</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
         <v>47</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
         <v>52</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
         <v>56</v>
@@ -1311,18 +1311,18 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
         <v>9</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B21" t="s">
         <v>57</v>
@@ -1342,33 +1342,33 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
         <v>61</v>
       </c>
       <c r="C22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" t="s">
         <v>8</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>9</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B23" t="s">
         <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23" t="s">
         <v>58</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B24" t="s">
         <v>64</v>
@@ -1402,27 +1402,27 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s">
         <v>66</v>
       </c>
-      <c r="C25" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>67</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>68</v>
-      </c>
-      <c r="F25" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B26" t="s">
         <v>69</v>
@@ -1431,24 +1431,24 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B27" t="s">
         <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D27" t="s">
         <v>58</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
         <v>71</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
         <v>72</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B30" t="s">
         <v>73</v>
@@ -1511,18 +1511,18 @@
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B31" t="s">
         <v>74</v>
@@ -1531,30 +1531,30 @@
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
         <v>76</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F32" t="s">
         <v>75</v>
@@ -1562,27 +1562,27 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B33" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s">
         <v>77</v>
-      </c>
-      <c r="C33" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" t="s">
-        <v>78</v>
       </c>
       <c r="E33" t="s">
         <v>53</v>
       </c>
       <c r="F33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B34" t="s">
         <v>80</v>
@@ -1591,18 +1591,18 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
         <v>9</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B35" t="s">
         <v>81</v>
@@ -1614,7 +1614,7 @@
         <v>46</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F35" t="s">
         <v>47</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B36" t="s">
         <v>82</v>
@@ -1631,18 +1631,18 @@
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B37" t="s">
         <v>84</v>
@@ -1651,10 +1651,10 @@
         <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F37" t="s">
         <v>83</v>
@@ -1662,7 +1662,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B38" t="s">
         <v>85</v>
@@ -1671,10 +1671,10 @@
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E38" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
         <v>86</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B39" t="s">
         <v>87</v>
@@ -1691,18 +1691,18 @@
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B40" t="s">
         <v>88</v>
@@ -1714,7 +1714,7 @@
         <v>46</v>
       </c>
       <c r="E40" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F40" t="s">
         <v>47</v>
@@ -1722,27 +1722,27 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41" t="s">
         <v>89</v>
-      </c>
-      <c r="C41" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" t="s">
-        <v>42</v>
-      </c>
-      <c r="E41" t="s">
-        <v>18</v>
-      </c>
-      <c r="F41" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B42" t="s">
         <v>91</v>
@@ -1754,7 +1754,7 @@
         <v>46</v>
       </c>
       <c r="E42" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F42" t="s">
         <v>47</v>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -1774,15 +1774,15 @@
         <v>46</v>
       </c>
       <c r="E43" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F43" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B44" t="s">
         <v>94</v>
@@ -1791,18 +1791,18 @@
         <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F44" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B45" t="s">
         <v>95</v>
@@ -1814,7 +1814,7 @@
         <v>46</v>
       </c>
       <c r="E45" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F45" t="s">
         <v>47</v>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B46" t="s">
         <v>96</v>
@@ -1831,10 +1831,10 @@
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F46" t="s">
         <v>97</v>
@@ -1842,27 +1842,27 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B47" t="s">
+        <v>99</v>
+      </c>
+      <c r="C47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" t="s">
+        <v>100</v>
+      </c>
+      <c r="E47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" t="s">
         <v>98</v>
-      </c>
-      <c r="C47" t="s">
-        <v>17</v>
-      </c>
-      <c r="D47" t="s">
-        <v>99</v>
-      </c>
-      <c r="E47" t="s">
-        <v>100</v>
-      </c>
-      <c r="F47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B48" t="s">
         <v>105</v>
@@ -1882,47 +1882,47 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B49" t="s">
+        <v>106</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s">
+        <v>107</v>
+      </c>
+      <c r="E49" t="s">
+        <v>108</v>
+      </c>
+      <c r="F49" t="s">
         <v>109</v>
-      </c>
-      <c r="C49" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" t="s">
-        <v>106</v>
-      </c>
-      <c r="E49" t="s">
-        <v>107</v>
-      </c>
-      <c r="F49" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" t="s">
         <v>110</v>
       </c>
-      <c r="C50" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>111</v>
       </c>
-      <c r="E50" t="s">
-        <v>112</v>
-      </c>
       <c r="F50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B51" t="s">
         <v>113</v>
@@ -1934,7 +1934,7 @@
         <v>46</v>
       </c>
       <c r="E51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F51" t="s">
         <v>47</v>
@@ -1942,10 +1942,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C52" t="s">
         <v>13</v>
@@ -1954,15 +1954,15 @@
         <v>59</v>
       </c>
       <c r="E52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F52" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B53" t="s">
         <v>116</v>
@@ -1971,18 +1971,18 @@
         <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F53" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B54" t="s">
         <v>117</v>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B55" t="s">
         <v>120</v>
@@ -2022,7 +2022,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B56" t="s">
         <v>121</v>
@@ -2031,18 +2031,18 @@
         <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E56" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B57" t="s">
         <v>122</v>
@@ -2051,18 +2051,18 @@
         <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E57" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F57" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B58" t="s">
         <v>123</v>
@@ -2071,18 +2071,18 @@
         <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F58" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B59" t="s">
         <v>124</v>
@@ -2102,27 +2102,27 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" t="s">
         <v>126</v>
       </c>
-      <c r="C60" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
+        <v>67</v>
+      </c>
+      <c r="F60" t="s">
         <v>127</v>
-      </c>
-      <c r="E60" t="s">
-        <v>68</v>
-      </c>
-      <c r="F60" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B61" t="s">
         <v>128</v>
@@ -2134,7 +2134,7 @@
         <v>46</v>
       </c>
       <c r="E61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F61" t="s">
         <v>47</v>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B62" t="s">
         <v>129</v>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B63" t="s">
         <v>131</v>
@@ -2171,10 +2171,10 @@
         <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E63" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F63" t="s">
         <v>130</v>
@@ -2182,7 +2182,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B64" t="s">
         <v>132</v>
@@ -2197,12 +2197,12 @@
         <v>134</v>
       </c>
       <c r="F64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B65" t="s">
         <v>135</v>
@@ -2211,7 +2211,7 @@
         <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E65" t="s">
         <v>54</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B66" t="s">
         <v>136</v>
@@ -2231,10 +2231,10 @@
         <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E66" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F66" t="s">
         <v>97</v>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B67" t="s">
         <v>137</v>
@@ -2262,67 +2262,67 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B68" t="s">
+        <v>139</v>
+      </c>
+      <c r="C68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" t="s">
         <v>140</v>
       </c>
-      <c r="C68" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
+        <v>126</v>
+      </c>
+      <c r="F68" t="s">
         <v>138</v>
-      </c>
-      <c r="E68" t="s">
-        <v>127</v>
-      </c>
-      <c r="F68" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B69" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D69" t="s">
         <v>102</v>
       </c>
       <c r="E69" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F69" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B70" t="s">
+        <v>144</v>
+      </c>
+      <c r="C70" t="s">
         <v>145</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>146</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
+        <v>126</v>
+      </c>
+      <c r="F70" t="s">
         <v>143</v>
-      </c>
-      <c r="E70" t="s">
-        <v>127</v>
-      </c>
-      <c r="F70" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B71" t="s">
         <v>147</v>
@@ -2331,10 +2331,10 @@
         <v>13</v>
       </c>
       <c r="D71" t="s">
+        <v>146</v>
+      </c>
+      <c r="E71" t="s">
         <v>143</v>
-      </c>
-      <c r="E71" t="s">
-        <v>144</v>
       </c>
       <c r="F71" t="s">
         <v>148</v>
@@ -2342,7 +2342,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B72" t="s">
         <v>149</v>
@@ -2351,7 +2351,7 @@
         <v>13</v>
       </c>
       <c r="D72" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E72" t="s">
         <v>102</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B73" t="s">
         <v>151</v>
@@ -2371,50 +2371,50 @@
         <v>13</v>
       </c>
       <c r="D73" t="s">
+        <v>146</v>
+      </c>
+      <c r="E73" t="s">
+        <v>126</v>
+      </c>
+      <c r="F73" t="s">
         <v>143</v>
-      </c>
-      <c r="E73" t="s">
-        <v>127</v>
-      </c>
-      <c r="F73" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>10</v>
+      </c>
+      <c r="B74" t="s">
+        <v>152</v>
+      </c>
+      <c r="C74" t="s">
         <v>6</v>
       </c>
-      <c r="B74" t="s">
+      <c r="D74" t="s">
+        <v>101</v>
+      </c>
+      <c r="E74" t="s">
+        <v>153</v>
+      </c>
+      <c r="F74" t="s">
         <v>154</v>
-      </c>
-      <c r="C74" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" t="s">
-        <v>100</v>
-      </c>
-      <c r="E74" t="s">
-        <v>152</v>
-      </c>
-      <c r="F74" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B75" t="s">
         <v>155</v>
       </c>
       <c r="C75" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D75" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E75" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F75" t="s">
         <v>97</v>
@@ -2422,7 +2422,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B76" t="s">
         <v>156</v>
@@ -2431,18 +2431,18 @@
         <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E76" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F76" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B77" t="s">
         <v>157</v>
@@ -2451,30 +2451,30 @@
         <v>158</v>
       </c>
       <c r="D77" t="s">
+        <v>66</v>
+      </c>
+      <c r="E77" t="s">
         <v>67</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>68</v>
-      </c>
-      <c r="F77" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B78" t="s">
+        <v>159</v>
+      </c>
+      <c r="C78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" t="s">
         <v>160</v>
       </c>
-      <c r="C78" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" t="s">
-        <v>159</v>
-      </c>
       <c r="E78" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F78" t="s">
         <v>23</v>
@@ -2482,16 +2482,16 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B79" t="s">
         <v>161</v>
       </c>
       <c r="C79" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D79" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E79" t="s">
         <v>26</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B80" t="s">
         <v>162</v>
@@ -2511,7 +2511,7 @@
         <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E80" t="s">
         <v>15</v>
@@ -2522,7 +2522,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B81" t="s">
         <v>164</v>
@@ -2542,7 +2542,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B82" t="s">
         <v>165</v>
@@ -2554,7 +2554,7 @@
         <v>46</v>
       </c>
       <c r="E82" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F82" t="s">
         <v>47</v>
@@ -2562,16 +2562,16 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B83" t="s">
         <v>166</v>
       </c>
       <c r="C83" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D83" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E83" t="s">
         <v>167</v>
@@ -2582,7 +2582,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B84" t="s">
         <v>168</v>
@@ -2591,24 +2591,24 @@
         <v>13</v>
       </c>
       <c r="D84" t="s">
+        <v>7</v>
+      </c>
+      <c r="E84" t="s">
+        <v>8</v>
+      </c>
+      <c r="F84" t="s">
         <v>9</v>
-      </c>
-      <c r="E84" t="s">
-        <v>10</v>
-      </c>
-      <c r="F84" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B85" t="s">
         <v>169</v>
       </c>
       <c r="C85" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D85" t="s">
         <v>54</v>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B86" t="s">
         <v>170</v>
@@ -2631,7 +2631,7 @@
         <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E86" t="s">
         <v>54</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B87" t="s">
         <v>171</v>
@@ -2654,35 +2654,35 @@
         <v>102</v>
       </c>
       <c r="E87" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F87" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B88" t="s">
         <v>172</v>
       </c>
       <c r="C88" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D88" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E88" t="s">
         <v>102</v>
       </c>
       <c r="F88" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B89" t="s">
         <v>173</v>
@@ -2702,7 +2702,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B90" t="s">
         <v>177</v>
@@ -2714,7 +2714,7 @@
         <v>59</v>
       </c>
       <c r="E90" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F90" t="s">
         <v>46</v>
@@ -2722,27 +2722,27 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B91" t="s">
+        <v>178</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" t="s">
         <v>179</v>
       </c>
-      <c r="C91" t="s">
-        <v>13</v>
-      </c>
-      <c r="D91" t="s">
-        <v>178</v>
-      </c>
       <c r="E91" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F91" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B92" t="s">
         <v>180</v>
@@ -2762,13 +2762,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B93" t="s">
         <v>181</v>
       </c>
       <c r="C93" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D93" t="s">
         <v>58</v>
@@ -2782,13 +2782,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B94" t="s">
         <v>182</v>
       </c>
       <c r="C94" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D94" t="s">
         <v>58</v>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B95" t="s">
         <v>184</v>
@@ -2811,7 +2811,7 @@
         <v>13</v>
       </c>
       <c r="D95" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E95" t="s">
         <v>97</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B96" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C96" t="s">
         <v>13</v>
@@ -2834,15 +2834,15 @@
         <v>46</v>
       </c>
       <c r="E96" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F96" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B97" t="s">
         <v>187</v>
@@ -2854,7 +2854,7 @@
         <v>46</v>
       </c>
       <c r="E97" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F97" t="s">
         <v>188</v>
@@ -2862,7 +2862,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B98" t="s">
         <v>189</v>
@@ -2874,7 +2874,7 @@
         <v>118</v>
       </c>
       <c r="E98" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F98" t="s">
         <v>167</v>
@@ -2882,7 +2882,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B99" t="s">
         <v>190</v>
@@ -2897,12 +2897,12 @@
         <v>134</v>
       </c>
       <c r="F99" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B100" t="s">
         <v>191</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B101" t="s">
         <v>192</v>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B102" t="s">
         <v>193</v>
@@ -2951,44 +2951,44 @@
         <v>13</v>
       </c>
       <c r="D102" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E102" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F102" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B103" t="s">
         <v>194</v>
       </c>
       <c r="C103" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D103" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E103" t="s">
         <v>195</v>
       </c>
       <c r="F103" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B104" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C104" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D104" t="s">
         <v>102</v>
@@ -2997,18 +2997,18 @@
         <v>104</v>
       </c>
       <c r="F104" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B105" t="s">
         <v>199</v>
       </c>
       <c r="C105" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D105" t="s">
         <v>195</v>
